--- a/data/trans_orig/IP16B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97849</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102517</t>
+          <t>102509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129608</t>
+          <t>130146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134724</t>
+          <t>134693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230714</t>
+          <t>229974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236610</t>
+          <t>236498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85064</t>
+          <t>84977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92257</t>
+          <t>92250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90616</t>
+          <t>90270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178097</t>
+          <t>178087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186145</t>
+          <t>186336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61777</t>
+          <t>61578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111013</t>
+          <t>111384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115315</t>
+          <t>115320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211534</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207892</t>
+          <t>207817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215531</t>
+          <t>215526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>420591</t>
+          <t>421813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430650</t>
+          <t>430671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113789</t>
+          <t>113763</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117430</t>
+          <t>117438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151979</t>
+          <t>151899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155415</t>
+          <t>155423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267334</t>
+          <t>267661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272129</t>
+          <t>272437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>66115</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63810</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>130584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137018</t>
+          <t>137050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>634062</t>
+          <t>634059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>644497</t>
+          <t>644021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>717884</t>
+          <t>718305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>729525</t>
+          <t>729503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1356688</t>
+          <t>1355624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1371931</t>
+          <t>1371396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>32624</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>119232</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>116511</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120451</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>101010</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98144</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>102509</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>133205</t>
+          <t>99455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130146</t>
+          <t>96439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>234214</t>
+          <t>218687</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229974</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236498</t>
+          <t>220697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>120969</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>120969</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120969</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>102930</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>102930</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>102930</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135307</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135307</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135307</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>238237</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>238237</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>238237</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89550</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>87071</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>90672</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>89823</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>84977</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>92250</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>95,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93292</t>
+          <t>91620</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90270</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>183115</t>
+          <t>181168</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178087</t>
+          <t>176665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186336</t>
+          <t>184027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93572</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93572</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93572</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95340</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189145</t>
+          <t>186737</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189145</t>
+          <t>186737</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189145</t>
+          <t>186737</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56643</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55372</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>50731</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47714</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>52453</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49795</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63457</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61578</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>63853</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114188</t>
+          <t>109095</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111384</t>
+          <t>105969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115320</t>
+          <t>110114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>196772</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>191830</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>199205</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>214762</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>211220</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>216169</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>176234</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>172759</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>177167</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>212707</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>207817</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>215526</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>548</t>
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>427469</t>
+          <t>373006</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>421813</t>
+          <t>367532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430671</t>
+          <t>375748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9245</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9722</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201075</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201075</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201075</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>216169</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>216169</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>216169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217539</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217539</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217539</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378242</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378242</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141398</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>139638</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>142291</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>116369</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>113763</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>117438</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>154269</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151899</t>
+          <t>113586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155423</t>
+          <t>117069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>270639</t>
+          <t>257563</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267661</t>
+          <t>255098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272437</t>
+          <t>258894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2948</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4021</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>117784</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>117784</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>117784</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>155801</t>
+          <t>117329</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155801</t>
+          <t>117329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155801</t>
+          <t>117329</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>273585</t>
+          <t>259915</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>273585</t>
+          <t>259915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273585</t>
+          <t>259915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64247</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>60224</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>66062</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>67333</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>66115</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>67712</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>68856</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>67487</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>69194</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>133101</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>128709</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>134914</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>67886</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>64127</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>69660</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>135220</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>130584</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>137050</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2237</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6260</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1597</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2576</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6968</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2261</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6020</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2639</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7275</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67712</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67712</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67712</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137859</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137859</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137859</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>667840</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>660657</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>671981</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>640029</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>634059</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>644021</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>724816</t>
+          <t>604782</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>718305</t>
+          <t>598143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>729503</t>
+          <t>608278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1364845</t>
+          <t>1272620</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1355624</t>
+          <t>1264500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1371396</t>
+          <t>1278371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7471</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18795</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15970</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32624</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>679452</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>679452</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>679452</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>919</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>650029</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>650029</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>650029</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>738219</t>
+          <t>613810</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>738219</t>
+          <t>613810</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>738219</t>
+          <t>613810</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1388248</t>
+          <t>1293261</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1388248</t>
+          <t>1293261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1388248</t>
+          <t>1293261</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
